--- a/04_Merchant_Banking/instances/benchmark_reference_principal.xlsx
+++ b/04_Merchant_Banking/instances/benchmark_reference_principal.xlsx
@@ -9,18 +9,26 @@
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Uses" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Operating Model" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Debt Schedule" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Covenants" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Management Equity" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Returns Waterfall" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Sensitivity" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Checks" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Sources" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="RefreshLog" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sources &amp; Uses" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Operating Model" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Debt Schedule" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Covenants" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Management Equity" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Returns Waterfall" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Sensitivity" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Checks" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Sources" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="RefreshLog" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" name="FS_DOMAIN" vbProcedure="false">'Institutional Surface'!$C$5</definedName>
+    <definedName function="false" hidden="false" name="FS_MATURITY" vbProcedure="false">'Institutional Surface'!$C$6</definedName>
+    <definedName function="false" hidden="false" name="FS_MODEL_ID" vbProcedure="false">'Institutional Surface'!$C$4</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -31,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="309">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Underwriting Model</t>
   </si>
@@ -102,6 +110,303 @@
     <t xml:space="preserve">PASS / REVIEW / FAIL must remain visible</t>
   </si>
   <si>
+    <t xml:space="preserve">Merchant Banking — Institutional Decision Surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchant Banking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declared maturity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools/builders/build_lbo_release.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">principal investing committee, client coverage, financing partners and risk committee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Committee artifact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">principal-and-advisory conflicts pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daily live transactions; weekly risk; monthly portfolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key decision outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">risk-adjusted principal return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client economics and fee offsets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">holdco / opco value and leakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base, downside and break-even outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liquidity / funding requirement and binding constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insider questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who owns the paper if distribution fails?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which economics are contractual versus relationship assumptions?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where can holdco cash be trapped?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which assumption is owner-approved versus modeler judgement?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What fails first and who must act?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario families</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client loss / failed process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">underwriting take-down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">holdco leakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data freshness / source failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">combined severe-but-plausible downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary diligence documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">engagement letters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conflicts memorandum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">financing and syndication papers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">approved model card and assumption register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">independent validation and challenge record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">principal and advisory cash flows separated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fees not double-counted in returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legal-entity exposure reconciles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source-to-model lineage is reproducible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">units, signs, dates and legal definitions reconcile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known failure modes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treating advisory fees as guaranteed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ignoring residual underwriting inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">failing to allocate shared expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stale vintage presented as current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision output disconnected from a binding constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory / methodological anchors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applicability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve SR 26-2 Model Risk Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">governance, validation, change control, monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.federalreserve.gov/supervisionreg/srletters/SR2602.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map explicitly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basel Framework</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prudential capital, liquidity, credit and market risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bis.org/basel_framework/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Challenge, Override and Closure Log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source, Transformation, Ownership and Refresh Map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System / provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As-of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downstream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">engagement status and probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TO MAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">principal exposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daily/weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legal-entity and concentration mapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model governance evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version, reviewer, sign-off and change log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision-use snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immutable as-of date and source receipt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transaction, Operating, and Financing Assumptions</t>
   </si>
   <si>
@@ -450,9 +755,6 @@
     <t xml:space="preserve">Cash headroom</t>
   </si>
   <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
     <t xml:space="preserve">Management Equity and Incentive Pool</t>
   </si>
   <si>
@@ -576,9 +878,6 @@
     <t xml:space="preserve">Source URL or document</t>
   </si>
   <si>
-    <t xml:space="preserve">As-of</t>
-  </si>
-  <si>
     <t xml:space="preserve">Notes / transformation</t>
   </si>
   <si>
@@ -640,9 +939,6 @@
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
   </si>
   <si>
     <t xml:space="preserve">Trigger</t>
@@ -684,7 +980,7 @@
     <numFmt numFmtId="168" formatCode="0.0\x;[RED]\(0.0&quot;x)&quot;;\-"/>
     <numFmt numFmtId="169" formatCode="0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -761,8 +1057,31 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -772,7 +1091,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor rgb="FF17365D"/>
       </patternFill>
     </fill>
     <fill>
@@ -787,8 +1106,20 @@
         <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+        <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -802,6 +1133,15 @@
       <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -840,7 +1180,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -878,6 +1218,30 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -941,11 +1305,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1018,11 +1382,11 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9EAF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFB7B7B7"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1047,7 +1411,7 @@
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF17365D"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF111827"/>
       <rgbColor rgb="FF333300"/>
@@ -1381,6 +1745,802 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <f aca="false">Assumptions!E30</f>
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <f aca="false">1-C5</f>
+        <v>0.9</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <f aca="false">'Sources &amp; Uses'!F8</f>
+        <v>1083.9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <f aca="false">C7*(1+Assumptions!E31)^Assumptions!E29</f>
+        <v>1857.61412493012</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <f aca="false">Assumptions!E32</f>
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:J15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <f aca="false">'Operating Model'!D8</f>
+        <v>173.9925</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <f aca="false">'Operating Model'!E8</f>
+        <v>186.736275</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <f aca="false">'Operating Model'!F8</f>
+        <v>200.2746549375</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <f aca="false">'Operating Model'!G8</f>
+        <v>214.6533481125</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <f aca="false">'Operating Model'!H8</f>
+        <v>229.920567497002</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <f aca="false">'Operating Model'!I8</f>
+        <v>246.12716359618</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <f aca="false">'Operating Model'!J8</f>
+        <v>263.326764195104</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <f aca="false">INDEX(C5:I5,1,Assumptions!E29)</f>
+        <v>263.326764195104</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="26" t="n">
+        <f aca="false">Assumptions!$E$28</f>
+        <v>10</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <f aca="false">Assumptions!$E$28</f>
+        <v>10</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <f aca="false">Assumptions!$E$28</f>
+        <v>10</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <f aca="false">Assumptions!$E$28</f>
+        <v>10</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <f aca="false">Assumptions!$E$28</f>
+        <v>10</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <f aca="false">Assumptions!$E$28</f>
+        <v>10</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <f aca="false">Assumptions!$E$28</f>
+        <v>10</v>
+      </c>
+      <c r="J6" s="26" t="n">
+        <f aca="false">INDEX(C6:I6,1,Assumptions!E29)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <f aca="false">C5*C6</f>
+        <v>1739.925</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <f aca="false">D5*D6</f>
+        <v>1867.36275</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <f aca="false">E5*E6</f>
+        <v>2002.746549375</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <f aca="false">F5*F6</f>
+        <v>2146.533481125</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <f aca="false">G5*G6</f>
+        <v>2299.20567497002</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <f aca="false">H5*H6</f>
+        <v>2461.2716359618</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <f aca="false">I5*I6</f>
+        <v>2633.26764195104</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <f aca="false">INDEX(C7:I7,1,Assumptions!E29)</f>
+        <v>2633.26764195104</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <f aca="false">'Debt Schedule'!D28</f>
+        <v>618.1</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <f aca="false">'Debt Schedule'!E28</f>
+        <v>556.22000078125</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <f aca="false">'Debt Schedule'!F28</f>
+        <v>481.318891647095</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <f aca="false">'Debt Schedule'!G28</f>
+        <v>391.860691915881</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <f aca="false">'Debt Schedule'!H28</f>
+        <v>286.169521543951</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <f aca="false">'Debt Schedule'!I28</f>
+        <v>162.408693611246</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <f aca="false">'Debt Schedule'!J28</f>
+        <v>18.5660354152367</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <f aca="false">INDEX(C8:I8,1,Assumptions!E29)</f>
+        <v>18.5660354152367</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <f aca="false">MAX(0,C7-C8)</f>
+        <v>1121.825</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <f aca="false">MAX(0,D7-D8)</f>
+        <v>1311.14274921875</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <f aca="false">MAX(0,E7-E8)</f>
+        <v>1521.4276577279</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <f aca="false">MAX(0,F7-F8)</f>
+        <v>1754.67278920912</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <f aca="false">MAX(0,G7-G8)</f>
+        <v>2013.03615342606</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <f aca="false">MAX(0,H7-H8)</f>
+        <v>2298.86294235056</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <f aca="false">MAX(0,I7-I8)</f>
+        <v>2614.7016065358</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <f aca="false">INDEX(C9:I9,1,Assumptions!E29)</f>
+        <v>2614.7016065358</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^1</f>
+        <v>1170.612</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^2</f>
+        <v>1264.26096</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^3</f>
+        <v>1365.4018368</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^4</f>
+        <v>1474.633983744</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^5</f>
+        <v>1592.60470244352</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^6</f>
+        <v>1720.013078639</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^7</f>
+        <v>1857.61412493012</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <f aca="false">INDEX(C10:I10,1,Assumptions!E29)</f>
+        <v>1857.61412493012</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <f aca="false">MAX(0,C9-C10)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <f aca="false">MAX(0,D9-D10)</f>
+        <v>46.8817892187492</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <f aca="false">MAX(0,E9-E10)</f>
+        <v>156.025820927905</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <f aca="false">MAX(0,F9-F10)</f>
+        <v>280.038805465118</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <f aca="false">MAX(0,G9-G10)</f>
+        <v>420.431450982544</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <f aca="false">MAX(0,H9-H10)</f>
+        <v>578.849863711556</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <f aca="false">MAX(0,I9-I10)</f>
+        <v>757.08748160568</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <f aca="false">INDEX(C11:I11,1,Assumptions!E29)</f>
+        <v>757.08748160568</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <f aca="false">MIN(C9,C9*Assumptions!$E$30+C11*Assumptions!$E$32)</f>
+        <v>112.1825</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <f aca="false">MIN(D9,D9*Assumptions!$E$30+D11*Assumptions!$E$32)</f>
+        <v>140.490632765625</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <f aca="false">MIN(E9,E9*Assumptions!$E$30+E11*Assumptions!$E$32)</f>
+        <v>183.347929958371</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <f aca="false">MIN(F9,F9*Assumptions!$E$30+F11*Assumptions!$E$32)</f>
+        <v>231.475040013935</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <f aca="false">MIN(G9,G9*Assumptions!$E$30+G11*Assumptions!$E$32)</f>
+        <v>285.389905539115</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <f aca="false">MIN(H9,H9*Assumptions!$E$30+H11*Assumptions!$E$32)</f>
+        <v>345.656266977367</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <f aca="false">MIN(I9,I9*Assumptions!$E$30+I11*Assumptions!$E$32)</f>
+        <v>412.887656974716</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <f aca="false">INDEX(C12:I12,1,Assumptions!E29)</f>
+        <v>412.887656974716</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <f aca="false">MAX(0,C9-C12)</f>
+        <v>1009.6425</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <f aca="false">MAX(0,D9-D12)</f>
+        <v>1170.65211645312</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <f aca="false">MAX(0,E9-E12)</f>
+        <v>1338.07972776953</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <f aca="false">MAX(0,F9-F12)</f>
+        <v>1523.19774919518</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <f aca="false">MAX(0,G9-G12)</f>
+        <v>1727.64624788695</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <f aca="false">MAX(0,H9-H12)</f>
+        <v>1953.20667537319</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <f aca="false">MAX(0,I9-I12)</f>
+        <v>2201.81394956109</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <f aca="false">INDEX(C13:I13,1,Assumptions!E29)</f>
+        <v>2201.81394956109</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C14" s="26" t="n">
+        <f aca="false">IFERROR(C13/'Sources &amp; Uses'!$F$8,0)</f>
+        <v>0.93149045114863</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <f aca="false">IFERROR(D13/'Sources &amp; Uses'!$F$8,0)</f>
+        <v>1.0800370112124</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <f aca="false">IFERROR(E13/'Sources &amp; Uses'!$F$8,0)</f>
+        <v>1.23450477698084</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <f aca="false">IFERROR(F13/'Sources &amp; Uses'!$F$8,0)</f>
+        <v>1.40529361490468</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <f aca="false">IFERROR(G13/'Sources &amp; Uses'!$F$8,0)</f>
+        <v>1.59391664165232</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <f aca="false">IFERROR(H13/'Sources &amp; Uses'!$F$8,0)</f>
+        <v>1.80201741431238</v>
+      </c>
+      <c r="I14" s="26" t="n">
+        <f aca="false">IFERROR(I13/'Sources &amp; Uses'!$F$8,0)</f>
+        <v>2.03138107718524</v>
+      </c>
+      <c r="J14" s="26" t="n">
+        <f aca="false">INDEX(C14:I14,1,Assumptions!E29)</f>
+        <v>2.03138107718524</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="24" t="n">
+        <f aca="false">IFERROR((C13/'Sources &amp; Uses'!$F$8)^(1/1)-1,0)</f>
+        <v>-0.0685095488513703</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <f aca="false">IFERROR((D13/'Sources &amp; Uses'!$F$8)^(1/2)-1,0)</f>
+        <v>0.0392482914166392</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <f aca="false">IFERROR((E13/'Sources &amp; Uses'!$F$8)^(1/3)-1,0)</f>
+        <v>0.07274769884445</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <f aca="false">IFERROR((F13/'Sources &amp; Uses'!$F$8)^(1/4)-1,0)</f>
+        <v>0.0887840955006745</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <f aca="false">IFERROR((G13/'Sources &amp; Uses'!$F$8)^(1/5)-1,0)</f>
+        <v>0.0977239027592107</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <f aca="false">IFERROR((H13/'Sources &amp; Uses'!$F$8)^(1/6)-1,0)</f>
+        <v>0.103129496380244</v>
+      </c>
+      <c r="I15" s="24" t="n">
+        <f aca="false">IFERROR((I13/'Sources &amp; Uses'!$F$8)^(1/7)-1,0)</f>
+        <v>0.106547854276197</v>
+      </c>
+      <c r="J15" s="24" t="n">
+        <f aca="false">INDEX(C15:I15,1,Assumptions!E29)</f>
+        <v>0.106547854276197</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:G9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="33" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0759620362720157</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.113835763725601</v>
+      </c>
+      <c r="E5" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.147164780213708</v>
+      </c>
+      <c r="F5" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.177017888195313</v>
+      </c>
+      <c r="G5" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.204117616094705</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0351695155188243</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0716073514064728</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.10367277814797</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.132394077119746</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.158466383813301</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.00219075882595887</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0374677466533251</v>
+      </c>
+      <c r="E7" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0685116229232259</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0963179096999034</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.121559596629277</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>-0.0253434630919046</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.00896432360994903</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0391552994006961</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0661976353385956</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0907458313298675</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>-0.0488831509456008</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>-0.015403958275933</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0140578517839125</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.040447067240178</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
+        <v>0.0644023806629515</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:G9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFCE4D6"/>
+        <color rgb="FFFFF2CC"/>
+        <color rgb="FFE2F0D9"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:C13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1391,21 +2551,21 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>167</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>139</v>
+      <c r="B4" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="C5" s="1" t="str">
         <f aca="false">IF(ABS('Sources &amp; Uses'!F10)&lt;0.000001,"PASS","FAIL")</f>
@@ -1414,7 +2574,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>170</v>
+        <v>268</v>
       </c>
       <c r="C6" s="1" t="str">
         <f aca="false">IF('Sources &amp; Uses'!F8&gt;0,"PASS","FAIL")</f>
@@ -1423,7 +2583,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>171</v>
+        <v>269</v>
       </c>
       <c r="C7" s="1" t="str">
         <f aca="false">IF(MIN('Debt Schedule'!D15:J25)&gt;=0,"PASS","FAIL")</f>
@@ -1432,7 +2592,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>270</v>
       </c>
       <c r="C8" s="1" t="str">
         <f aca="false">IF(MIN('Debt Schedule'!D13:J13)&gt;=Assumptions!E16,"PASS","REVIEW")</f>
@@ -1441,7 +2601,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>173</v>
+        <v>271</v>
       </c>
       <c r="C9" s="1" t="str">
         <f aca="false">IF(COUNTIF(Covenants!C13:I13,"BREACH")=0,"PASS","REVIEW")</f>
@@ -1450,7 +2610,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>174</v>
+        <v>272</v>
       </c>
       <c r="C10" s="1" t="str">
         <f aca="false">IF(MIN('Returns Waterfall'!C9:I9)&gt;=0,"PASS","FAIL")</f>
@@ -1459,7 +2619,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>175</v>
+        <v>273</v>
       </c>
       <c r="C11" s="1" t="str">
         <f aca="false">IF(MAX(ABS('Returns Waterfall'!C9:I9-'Returns Waterfall'!C12:I12-'Returns Waterfall'!C13:I13))&lt;0.000001,"PASS","FAIL")</f>
@@ -1468,7 +2628,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>176</v>
+        <v>274</v>
       </c>
       <c r="C12" s="1" t="str">
         <f aca="false">IF(AND(Assumptions!E29&gt;=1,Assumptions!E29&lt;=7),"PASS","FAIL")</f>
@@ -1477,7 +2637,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>177</v>
+        <v>275</v>
       </c>
       <c r="C13" s="1" t="str">
         <f aca="false">IF(COUNTIF(C5:C12,"FAIL")=0,"PASS","FAIL")</f>
@@ -1512,7 +2672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1529,108 +2689,108 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>178</v>
+        <v>276</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>182</v>
+      <c r="B4" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>186</v>
+      <c r="B5" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="28" t="s">
+      <c r="B6" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="28" t="s">
-        <v>189</v>
+      <c r="E6" s="34" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="28" t="s">
+      <c r="B7" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="D7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="28" t="s">
-        <v>192</v>
+      <c r="E7" s="34" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="28" t="s">
+      <c r="B8" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="D8" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="28" t="s">
-        <v>195</v>
+      <c r="E8" s="34" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="28" t="s">
+      <c r="B9" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="28" t="s">
-        <v>198</v>
+      <c r="E9" s="34" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="D10" s="29" t="s">
+      <c r="B10" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="D10" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="29" t="s">
-        <v>201</v>
+      <c r="E10" s="35" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -1647,7 +2807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1666,7 +2826,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>202</v>
+        <v>299</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1675,236 +2835,236 @@
       <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>208</v>
+      <c r="B4" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>212</v>
+      <c r="C5" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1925,6 +3085,1070 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:F63"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F63" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B60:F60"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F14:F18" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F22:F26" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F30:F34" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F38:F42" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F46:F50" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F54:F58" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H54" type="list">
+      <formula1>"OPEN,IN REVIEW,REMEDIATED,ACCEPTED RISK,CLOSED"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G54" type="list">
+      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:J8"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J40" type="list">
+      <formula1>"TO MAP,ACTIVE,STALE,EXCEPTION,RETIRED"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1936,7 +4160,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1944,524 +4168,524 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>27</v>
+      <c r="D4" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="C5" s="17" t="n">
         <v>900</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="18" t="n">
         <v>600</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="19" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D5,C5)</f>
         <v>900</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="14" t="n">
+        <v>129</v>
+      </c>
+      <c r="C6" s="20" t="n">
         <v>0.18</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="21" t="n">
         <v>0.17</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D6,C6)</f>
         <v>0.18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="14" t="n">
+        <v>131</v>
+      </c>
+      <c r="C7" s="20" t="n">
         <v>0.045</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="21" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D7,C7)</f>
         <v>0.045</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="C8" s="23" t="n">
         <v>0.005</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="23" t="n">
         <v>-0.003</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D8,C8)</f>
         <v>0.005</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="15" t="n">
+        <v>134</v>
+      </c>
+      <c r="C9" s="21" t="n">
         <v>0.025</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="21" t="n">
         <v>0.025</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D9,C9)</f>
         <v>0.025</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="15" t="n">
+        <v>135</v>
+      </c>
+      <c r="C10" s="21" t="n">
         <v>0.035</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="21" t="n">
         <v>0.045</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D10,C10)</f>
         <v>0.035</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="15" t="n">
+        <v>136</v>
+      </c>
+      <c r="C11" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D11,C11)</f>
         <v>0.08</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="15" t="n">
+        <v>137</v>
+      </c>
+      <c r="C12" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D12,C12)</f>
         <v>0.25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="19" t="n">
+        <v>138</v>
+      </c>
+      <c r="C13" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D13,C13)</f>
         <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="C14" s="21" t="n">
         <v>0.02</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="21" t="n">
         <v>0.025</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D14,C14)</f>
         <v>0.02</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="12" t="n">
+        <v>141</v>
+      </c>
+      <c r="C15" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="19" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D15,C15)</f>
         <v>100</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="C16" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="19" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D16,C16)</f>
         <v>20</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="12" t="n">
+        <v>143</v>
+      </c>
+      <c r="C17" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="19" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D17,C17)</f>
         <v>75</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="17" t="n">
+        <v>144</v>
+      </c>
+      <c r="C18" s="23" t="n">
         <v>0.09</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="23" t="n">
         <v>0.115</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D18,C18)</f>
         <v>0.09</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="21" t="n">
+        <v>145</v>
+      </c>
+      <c r="C19" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E19" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D19,C19)</f>
         <v>3.5</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="17" t="n">
+        <v>147</v>
+      </c>
+      <c r="C20" s="23" t="n">
         <v>0.085</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="23" t="n">
         <v>0.105</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D20,C20)</f>
         <v>0.085</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="15" t="n">
+        <v>148</v>
+      </c>
+      <c r="C21" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D21,C21)</f>
         <v>0.01</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="C22" s="27" t="n">
         <v>0.75</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D22,C22)</f>
         <v>0.75</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="17" t="n">
+        <v>151</v>
+      </c>
+      <c r="C23" s="23" t="n">
         <v>0.11</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="23" t="n">
         <v>0.13</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D23,C23)</f>
         <v>0.11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="17" t="n">
+        <v>152</v>
+      </c>
+      <c r="C24" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D24,C24)</f>
         <v>0.03</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="15" t="n">
+        <v>153</v>
+      </c>
+      <c r="C25" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D25,C25)</f>
         <v>0.75</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="19" t="n">
+        <v>155</v>
+      </c>
+      <c r="C26" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="19" t="n">
+      <c r="D26" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="E26" s="20" t="n">
+      <c r="E26" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D26,C26)</f>
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="19" t="n">
+        <v>156</v>
+      </c>
+      <c r="C27" s="25" t="n">
         <v>1.75</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="E27" s="20" t="n">
+      <c r="E27" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D27,C27)</f>
         <v>1.75</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="19" t="n">
+        <v>157</v>
+      </c>
+      <c r="C28" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="20" t="n">
+      <c r="E28" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D28,C28)</f>
         <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="22" t="n">
+        <v>158</v>
+      </c>
+      <c r="C29" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="30" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D29,C29)</f>
         <v>7</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="C30" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D30,C30)</f>
         <v>0.1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="15" t="n">
+        <v>162</v>
+      </c>
+      <c r="C31" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D31,C31)</f>
         <v>0.08</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="15" t="n">
+        <v>163</v>
+      </c>
+      <c r="C32" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D32" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="22" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D32,C32)</f>
         <v>0.2</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>65</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2478,7 +4702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2497,7 +4721,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2506,105 +4730,105 @@
       <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="10"/>
+      <c r="B4" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="13" t="n">
+        <v>169</v>
+      </c>
+      <c r="C5" s="19" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E13</f>
         <v>1620</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="12" t="n">
+        <v>170</v>
+      </c>
+      <c r="F5" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="13" t="n">
+        <v>171</v>
+      </c>
+      <c r="C6" s="19" t="n">
         <f aca="false">Assumptions!E15</f>
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="13" t="n">
+        <v>172</v>
+      </c>
+      <c r="F6" s="19" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E19</f>
         <v>567</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="13" t="n">
+        <v>173</v>
+      </c>
+      <c r="C7" s="19" t="n">
         <f aca="false">C5*Assumptions!E14</f>
         <v>32.4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="13" t="n">
+        <v>174</v>
+      </c>
+      <c r="F7" s="19" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E22</f>
         <v>121.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="C8" s="19" t="n">
         <f aca="false">Assumptions!E16</f>
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="13" t="n">
+        <v>176</v>
+      </c>
+      <c r="F8" s="19" t="n">
         <f aca="false">C9-SUM(F5:F7)</f>
         <v>1083.9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="26" t="n">
+      <c r="B9" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="32" t="n">
         <f aca="false">SUM(C5:C8)</f>
         <v>1772.4</v>
       </c>
-      <c r="E9" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="26" t="n">
+      <c r="E9" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="F9" s="32" t="n">
         <f aca="false">SUM(F5:F8)</f>
         <v>1772.4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="13" t="n">
+        <v>179</v>
+      </c>
+      <c r="F10" s="19" t="n">
         <f aca="false">F9-C9</f>
         <v>0</v>
       </c>
@@ -2623,7 +4847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2638,7 +4862,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2649,551 +4873,551 @@
       <c r="I2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>90</v>
+      <c r="B4" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="C5" s="19" t="n">
         <f aca="false">Assumptions!E5</f>
         <v>900</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="19" t="n">
         <f aca="false">C5*(1+Assumptions!$E$7)</f>
         <v>940.5</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="19" t="n">
         <f aca="false">D5*(1+Assumptions!$E$7)</f>
         <v>982.8225</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="19" t="n">
         <f aca="false">E5*(1+Assumptions!$E$7)</f>
         <v>1027.0495125</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="19" t="n">
         <f aca="false">F5*(1+Assumptions!$E$7)</f>
         <v>1073.2667405625</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="19" t="n">
         <f aca="false">G5*(1+Assumptions!$E$7)</f>
         <v>1121.56374388781</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="19" t="n">
         <f aca="false">H5*(1+Assumptions!$E$7)</f>
         <v>1172.03411236276</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="19" t="n">
         <f aca="false">I5*(1+Assumptions!$E$7)</f>
         <v>1224.77564741909</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="16" t="n">
+        <v>191</v>
+      </c>
+      <c r="D6" s="22" t="n">
         <f aca="false">IFERROR(D5/C5-1,0)</f>
         <v>0.0449999999999999</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="22" t="n">
         <f aca="false">IFERROR(E5/D5-1,0)</f>
         <v>0.0449999999999999</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="22" t="n">
         <f aca="false">IFERROR(F5/E5-1,0)</f>
         <v>0.0449999999999999</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="22" t="n">
         <f aca="false">IFERROR(G5/F5-1,0)</f>
         <v>0.0449999999999999</v>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="H6" s="22" t="n">
         <f aca="false">IFERROR(H5/G5-1,0)</f>
         <v>0.0449999999999999</v>
       </c>
-      <c r="I6" s="16" t="n">
+      <c r="I6" s="22" t="n">
         <f aca="false">IFERROR(I5/H5-1,0)</f>
         <v>0.0449999999999999</v>
       </c>
-      <c r="J6" s="16" t="n">
+      <c r="J6" s="22" t="n">
         <f aca="false">IFERROR(J5/I5-1,0)</f>
         <v>0.0449999999999999</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="16" t="n">
+        <v>192</v>
+      </c>
+      <c r="C7" s="22" t="n">
         <f aca="false">Assumptions!E6</f>
         <v>0.18</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="22" t="n">
         <f aca="false">MAX(0,MIN(0.6,C7+Assumptions!$E$8))</f>
         <v>0.185</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="22" t="n">
         <f aca="false">MAX(0,MIN(0.6,D7+Assumptions!$E$8))</f>
         <v>0.19</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="22" t="n">
         <f aca="false">MAX(0,MIN(0.6,E7+Assumptions!$E$8))</f>
         <v>0.195</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="22" t="n">
         <f aca="false">MAX(0,MIN(0.6,F7+Assumptions!$E$8))</f>
         <v>0.2</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="22" t="n">
         <f aca="false">MAX(0,MIN(0.6,G7+Assumptions!$E$8))</f>
         <v>0.205</v>
       </c>
-      <c r="I7" s="16" t="n">
+      <c r="I7" s="22" t="n">
         <f aca="false">MAX(0,MIN(0.6,H7+Assumptions!$E$8))</f>
         <v>0.21</v>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="J7" s="22" t="n">
         <f aca="false">MAX(0,MIN(0.6,I7+Assumptions!$E$8))</f>
         <v>0.215</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="26" t="n">
+      <c r="B8" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="32" t="n">
         <f aca="false">C5*C7</f>
         <v>162</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="32" t="n">
         <f aca="false">D5*D7</f>
         <v>173.9925</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="32" t="n">
         <f aca="false">E5*E7</f>
         <v>186.736275</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="32" t="n">
         <f aca="false">F5*F7</f>
         <v>200.2746549375</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="32" t="n">
         <f aca="false">G5*G7</f>
         <v>214.6533481125</v>
       </c>
-      <c r="H8" s="26" t="n">
+      <c r="H8" s="32" t="n">
         <f aca="false">H5*H7</f>
         <v>229.920567497002</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="32" t="n">
         <f aca="false">I5*I7</f>
         <v>246.12716359618</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="32" t="n">
         <f aca="false">J5*J7</f>
         <v>263.326764195104</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="13" t="n">
+        <v>194</v>
+      </c>
+      <c r="C9" s="19" t="n">
         <f aca="false">C5*Assumptions!E9</f>
         <v>22.5</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="19" t="n">
         <f aca="false">D5*Assumptions!$E$9</f>
         <v>23.5125</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">E5*Assumptions!$E$9</f>
         <v>24.5705625</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="19" t="n">
         <f aca="false">F5*Assumptions!$E$9</f>
         <v>25.6762378125</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="19" t="n">
         <f aca="false">G5*Assumptions!$E$9</f>
         <v>26.8316685140625</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="19" t="n">
         <f aca="false">H5*Assumptions!$E$9</f>
         <v>28.0390935971953</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="19" t="n">
         <f aca="false">I5*Assumptions!$E$9</f>
         <v>29.3008528090691</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="19" t="n">
         <f aca="false">J5*Assumptions!$E$9</f>
         <v>30.6193911854772</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="13" t="n">
+        <v>195</v>
+      </c>
+      <c r="C10" s="19" t="n">
         <f aca="false">C8-C9</f>
         <v>139.5</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="19" t="n">
         <f aca="false">D8-D9</f>
         <v>150.48</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="19" t="n">
         <f aca="false">E8-E9</f>
         <v>162.1657125</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">F8-F9</f>
         <v>174.598417125</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="19" t="n">
         <f aca="false">G8-G9</f>
         <v>187.821679598437</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="19" t="n">
         <f aca="false">H8-H9</f>
         <v>201.881473899806</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="19" t="n">
         <f aca="false">I8-I9</f>
         <v>216.826310787111</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="19" t="n">
         <f aca="false">J8-J9</f>
         <v>232.707373009627</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="13" t="n">
+        <v>196</v>
+      </c>
+      <c r="D11" s="19" t="n">
         <f aca="false">'Debt Schedule'!D7</f>
         <v>61.56</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">'Debt Schedule'!E7</f>
         <v>57.397359375</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="19" t="n">
         <f aca="false">'Debt Schedule'!F7</f>
         <v>52.0068205678711</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="19" t="n">
         <f aca="false">'Debt Schedule'!G7</f>
         <v>45.4356380415008</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="19" t="n">
         <f aca="false">'Debt Schedule'!H7</f>
         <v>37.5555938209532</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="19" t="n">
         <f aca="false">'Debt Schedule'!I7</f>
         <v>28.2154225430562</v>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J11" s="19" t="n">
         <f aca="false">'Debt Schedule'!J7</f>
         <v>17.2486087387356</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="13" t="n">
+        <v>197</v>
+      </c>
+      <c r="D12" s="19" t="n">
         <f aca="false">D10-D11</f>
         <v>88.92</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="19" t="n">
         <f aca="false">E10-E11</f>
         <v>104.768353125</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="19" t="n">
         <f aca="false">F10-F11</f>
         <v>122.591596557129</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="19" t="n">
         <f aca="false">G10-G11</f>
         <v>142.386041556937</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="19" t="n">
         <f aca="false">H10-H11</f>
         <v>164.325880078853</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="19" t="n">
         <f aca="false">I10-I11</f>
         <v>188.610888244055</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="19" t="n">
         <f aca="false">J10-J11</f>
         <v>215.458764270891</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" s="13" t="n">
+        <v>198</v>
+      </c>
+      <c r="D13" s="19" t="n">
         <f aca="false">MAX(0,D12*Assumptions!$E$12)</f>
         <v>22.23</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="19" t="n">
         <f aca="false">MAX(0,E12*Assumptions!$E$12)</f>
         <v>26.19208828125</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="19" t="n">
         <f aca="false">MAX(0,F12*Assumptions!$E$12)</f>
         <v>30.6478991392822</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="19" t="n">
         <f aca="false">MAX(0,G12*Assumptions!$E$12)</f>
         <v>35.5965103892342</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="19" t="n">
         <f aca="false">MAX(0,H12*Assumptions!$E$12)</f>
         <v>41.0814700197133</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="19" t="n">
         <f aca="false">MAX(0,I12*Assumptions!$E$12)</f>
         <v>47.1527220610138</v>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="19" t="n">
         <f aca="false">MAX(0,J12*Assumptions!$E$12)</f>
         <v>53.8646910677228</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="13" t="n">
+        <v>199</v>
+      </c>
+      <c r="D14" s="19" t="n">
         <f aca="false">D12-D13</f>
         <v>66.69</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="19" t="n">
         <f aca="false">E12-E13</f>
         <v>78.57626484375</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="19" t="n">
         <f aca="false">F12-F13</f>
         <v>91.9436974178467</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="19" t="n">
         <f aca="false">G12-G13</f>
         <v>106.789531167703</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="19" t="n">
         <f aca="false">H12-H13</f>
         <v>123.24441005914</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="I14" s="19" t="n">
         <f aca="false">I12-I13</f>
         <v>141.458166183041</v>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="19" t="n">
         <f aca="false">J12-J13</f>
         <v>161.594073203168</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="D15" s="19" t="n">
         <f aca="false">D5*Assumptions!$E$10</f>
         <v>32.9175</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="19" t="n">
         <f aca="false">E5*Assumptions!$E$10</f>
         <v>34.3987875</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="19" t="n">
         <f aca="false">F5*Assumptions!$E$10</f>
         <v>35.9467329375</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="19" t="n">
         <f aca="false">G5*Assumptions!$E$10</f>
         <v>37.5643359196875</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="19" t="n">
         <f aca="false">H5*Assumptions!$E$10</f>
         <v>39.2547310360734</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="19" t="n">
         <f aca="false">I5*Assumptions!$E$10</f>
         <v>41.0211939326967</v>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J15" s="19" t="n">
         <f aca="false">J5*Assumptions!$E$10</f>
         <v>42.8671476596681</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="13" t="n">
+        <v>201</v>
+      </c>
+      <c r="C16" s="19" t="n">
         <f aca="false">C5*Assumptions!E11</f>
         <v>72</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="19" t="n">
         <f aca="false">D5*Assumptions!$E$11</f>
         <v>75.24</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="19" t="n">
         <f aca="false">E5*Assumptions!$E$11</f>
         <v>78.6258</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="19" t="n">
         <f aca="false">F5*Assumptions!$E$11</f>
         <v>82.163961</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="19" t="n">
         <f aca="false">G5*Assumptions!$E$11</f>
         <v>85.861339245</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="19" t="n">
         <f aca="false">H5*Assumptions!$E$11</f>
         <v>89.725099511025</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="19" t="n">
         <f aca="false">I5*Assumptions!$E$11</f>
         <v>93.7627289890211</v>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="19" t="n">
         <f aca="false">J5*Assumptions!$E$11</f>
         <v>97.9820517935271</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="13" t="n">
+        <v>202</v>
+      </c>
+      <c r="D17" s="19" t="n">
         <f aca="false">D16-C16</f>
         <v>3.24</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="19" t="n">
         <f aca="false">E16-D16</f>
         <v>3.38579999999999</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="19" t="n">
         <f aca="false">F16-E16</f>
         <v>3.538161</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="19" t="n">
         <f aca="false">G16-F16</f>
         <v>3.697378245</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="19" t="n">
         <f aca="false">H16-G16</f>
         <v>3.863760266025</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="19" t="n">
         <f aca="false">I16-H16</f>
         <v>4.03762947799613</v>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="19" t="n">
         <f aca="false">J16-I16</f>
         <v>4.21932280450594</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26" t="n">
+      <c r="B18" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32" t="n">
         <f aca="false">D14+D9-D15-D17</f>
         <v>54.045</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="32" t="n">
         <f aca="false">E14+E9-E15-E17</f>
         <v>65.36223984375</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="32" t="n">
         <f aca="false">F14+F9-F15-F17</f>
         <v>78.1350412928466</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="32" t="n">
         <f aca="false">G14+G9-G15-G17</f>
         <v>92.3594855170775</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="32" t="n">
         <f aca="false">H14+H9-H15-H17</f>
         <v>108.165012354237</v>
       </c>
-      <c r="I18" s="26" t="n">
+      <c r="I18" s="32" t="n">
         <f aca="false">I14+I9-I15-I17</f>
         <v>125.700195581418</v>
       </c>
-      <c r="J18" s="26" t="n">
+      <c r="J18" s="32" t="n">
         <f aca="false">J14+J9-J15-J17</f>
         <v>145.126993924472</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26" t="n">
+      <c r="B19" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32" t="n">
         <f aca="false">D8-D13-D15-D17</f>
         <v>115.605</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="32" t="n">
         <f aca="false">E8-E13-E15-E17</f>
         <v>122.75959921875</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="32" t="n">
         <f aca="false">F8-F13-F15-F17</f>
         <v>130.141861860718</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="32" t="n">
         <f aca="false">G8-G13-G15-G17</f>
         <v>137.795123558578</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="32" t="n">
         <f aca="false">H8-H13-H15-H17</f>
         <v>145.72060617519</v>
       </c>
-      <c r="I19" s="26" t="n">
+      <c r="I19" s="32" t="n">
         <f aca="false">I8-I13-I15-I17</f>
         <v>153.915618124474</v>
       </c>
-      <c r="J19" s="26" t="n">
+      <c r="J19" s="32" t="n">
         <f aca="false">J8-J13-J15-J17</f>
         <v>162.375602663207</v>
       </c>
@@ -3212,7 +5436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3227,7 +5451,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>205</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3238,871 +5462,871 @@
       <c r="I2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>90</v>
+      <c r="B4" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="13" t="n">
+        <v>207</v>
+      </c>
+      <c r="C5" s="19" t="n">
         <f aca="false">Assumptions!E16</f>
         <v>20</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="19" t="n">
         <f aca="false">C13</f>
         <v>20</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="19" t="n">
         <f aca="false">D13</f>
         <v>23.0234375</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="19" t="n">
         <f aca="false">E13</f>
         <v>23.9197298339844</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="19" t="n">
         <f aca="false">F13</f>
         <v>24.7740481954269</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="19" t="n">
         <f aca="false">G13</f>
         <v>25.7164708570315</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="19" t="n">
         <f aca="false">H13</f>
         <v>26.7632177007043</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="19" t="n">
         <f aca="false">I13</f>
         <v>27.9245883301326</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="13" t="n">
+        <v>204</v>
+      </c>
+      <c r="D6" s="19" t="n">
         <f aca="false">'Operating Model'!D19</f>
         <v>115.605</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="19" t="n">
         <f aca="false">'Operating Model'!E19</f>
         <v>122.75959921875</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="19" t="n">
         <f aca="false">'Operating Model'!F19</f>
         <v>130.141861860718</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="19" t="n">
         <f aca="false">'Operating Model'!G19</f>
         <v>137.795123558578</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="19" t="n">
         <f aca="false">'Operating Model'!H19</f>
         <v>145.72060617519</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="19" t="n">
         <f aca="false">'Operating Model'!I19</f>
         <v>153.915618124474</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="19" t="n">
         <f aca="false">'Operating Model'!J19</f>
         <v>162.375602663207</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" s="13" t="n">
+        <v>196</v>
+      </c>
+      <c r="D7" s="19" t="n">
         <f aca="false">SUM(D15,D18,D23)</f>
         <v>61.56</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="19" t="n">
         <f aca="false">SUM(E15,E18,E23)</f>
         <v>57.397359375</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="19" t="n">
         <f aca="false">SUM(F15,F18,F23)</f>
         <v>52.0068205678711</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="19" t="n">
         <f aca="false">SUM(G15,G18,G23)</f>
         <v>45.4356380415008</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="19" t="n">
         <f aca="false">SUM(H15,H18,H23)</f>
         <v>37.5555938209532</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="19" t="n">
         <f aca="false">SUM(I15,I18,I23)</f>
         <v>28.2154225430562</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="19" t="n">
         <f aca="false">SUM(J15,J18,J23)</f>
         <v>17.2486087387356</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="13" t="n">
+        <v>208</v>
+      </c>
+      <c r="D8" s="19" t="n">
         <f aca="false">D19</f>
         <v>5.67</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="19" t="n">
         <f aca="false">E19</f>
         <v>5.67</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="19" t="n">
         <f aca="false">F19</f>
         <v>5.67</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="19" t="n">
         <f aca="false">G19</f>
         <v>5.67</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="19" t="n">
         <f aca="false">H19</f>
         <v>5.67</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="19" t="n">
         <f aca="false">I19</f>
         <v>5.67</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="19" t="n">
         <f aca="false">J19</f>
         <v>5.67</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="13" t="n">
+        <v>209</v>
+      </c>
+      <c r="D9" s="19" t="n">
         <f aca="false">D5+D6-D7-D8</f>
         <v>68.375</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">E5+E6-E7-E8</f>
         <v>82.71567734375</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="19" t="n">
         <f aca="false">F5+F6-F7-F8</f>
         <v>96.384771126831</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="19" t="n">
         <f aca="false">G5+G6-G7-G8</f>
         <v>111.463533712504</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="19" t="n">
         <f aca="false">H5+H6-H7-H8</f>
         <v>128.211483211268</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="19" t="n">
         <f aca="false">I5+I6-I7-I8</f>
         <v>146.793413282122</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="19" t="n">
         <f aca="false">J5+J6-J7-J8</f>
         <v>167.381582254604</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" s="13" t="n">
+        <v>210</v>
+      </c>
+      <c r="D10" s="19" t="n">
         <f aca="false">IF(D9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-D14,Assumptions!$E$16-D9),-MIN(D14,MAX(0,D9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="19" t="n">
         <f aca="false">IF(E9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-E14,Assumptions!$E$16-E9),-MIN(E14,MAX(0,E9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">IF(F9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-F14,Assumptions!$E$16-F9),-MIN(F14,MAX(0,F9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="19" t="n">
         <f aca="false">IF(G9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-G14,Assumptions!$E$16-G9),-MIN(G14,MAX(0,G9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="19" t="n">
         <f aca="false">IF(H9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-H14,Assumptions!$E$16-H9),-MIN(H14,MAX(0,H9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="19" t="n">
         <f aca="false">IF(I9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-I14,Assumptions!$E$16-I9),-MIN(I14,MAX(0,I9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="19" t="n">
         <f aca="false">IF(J9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-J14,Assumptions!$E$16-J9),-MIN(J14,MAX(0,J9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="13" t="n">
+        <v>211</v>
+      </c>
+      <c r="D11" s="19" t="n">
         <f aca="false">MIN(MAX(0,D17-D19),MAX(0,D9+D10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>36.28125</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">MIN(MAX(0,E17-E19),MAX(0,E9+E10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>47.0367580078125</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="19" t="n">
         <f aca="false">MIN(MAX(0,F17-F19),MAX(0,F9+F10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>57.2885783451233</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="19" t="n">
         <f aca="false">MIN(MAX(0,G17-G19),MAX(0,G9+G10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>68.5976502843784</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="19" t="n">
         <f aca="false">MIN(MAX(0,H17-H19),MAX(0,H9+H10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>81.1586124084512</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="19" t="n">
         <f aca="false">MIN(MAX(0,I17-I19),MAX(0,I9+I10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>95.0950599615914</v>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J11" s="19" t="n">
         <f aca="false">MIN(MAX(0,J17-J19),MAX(0,J9+J10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>110.536186690953</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="13" t="n">
+        <v>212</v>
+      </c>
+      <c r="D12" s="19" t="n">
         <f aca="false">MIN(MAX(0,D22+D24),MAX(0,D9+D10-D11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>9.0703125</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="19" t="n">
         <f aca="false">MIN(MAX(0,E22+E24),MAX(0,E9+E10-E11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>11.7591895019531</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="19" t="n">
         <f aca="false">MIN(MAX(0,F22+F24),MAX(0,F9+F10-F11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>14.3221445862808</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="19" t="n">
         <f aca="false">MIN(MAX(0,G22+G24),MAX(0,G9+G10-G11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>17.1494125710946</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="19" t="n">
         <f aca="false">MIN(MAX(0,H22+H24),MAX(0,H9+H10-H11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>20.2896531021128</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="19" t="n">
         <f aca="false">MIN(MAX(0,I22+I24),MAX(0,I9+I10-I11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>23.7737649903978</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="19" t="n">
         <f aca="false">MIN(MAX(0,J22+J24),MAX(0,J9+J10-J11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v>27.6340466727383</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="26" t="n">
+      <c r="B13" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="32" t="n">
         <f aca="false">C5</f>
         <v>20</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="32" t="n">
         <f aca="false">D9+D10-D11-D12</f>
         <v>23.0234375</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="32" t="n">
         <f aca="false">E9+E10-E11-E12</f>
         <v>23.9197298339844</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="32" t="n">
         <f aca="false">F9+F10-F11-F12</f>
         <v>24.7740481954269</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="32" t="n">
         <f aca="false">G9+G10-G11-G12</f>
         <v>25.7164708570315</v>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="32" t="n">
         <f aca="false">H9+H10-H11-H12</f>
         <v>26.7632177007043</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="32" t="n">
         <f aca="false">I9+I10-I11-I12</f>
         <v>27.9245883301326</v>
       </c>
-      <c r="J13" s="26" t="n">
+      <c r="J13" s="32" t="n">
         <f aca="false">J9+J10-J11-J12</f>
         <v>29.2113488909128</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="13" t="n">
+        <v>214</v>
+      </c>
+      <c r="C14" s="19" t="n">
         <f aca="false">'Sources &amp; Uses'!F5</f>
         <v>0</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="19" t="n">
         <f aca="false">C16</f>
         <v>0</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="19" t="n">
         <f aca="false">D16</f>
         <v>0</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="19" t="n">
         <f aca="false">E16</f>
         <v>0</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="19" t="n">
         <f aca="false">F16</f>
         <v>0</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="19" t="n">
         <f aca="false">G16</f>
         <v>0</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="I14" s="19" t="n">
         <f aca="false">H16</f>
         <v>0</v>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="19" t="n">
         <f aca="false">I16</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" s="13" t="n">
+        <v>215</v>
+      </c>
+      <c r="D15" s="19" t="n">
         <f aca="false">D14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="19" t="n">
         <f aca="false">E14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="19" t="n">
         <f aca="false">F14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="19" t="n">
         <f aca="false">G14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="19" t="n">
         <f aca="false">H14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="19" t="n">
         <f aca="false">I14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J15" s="19" t="n">
         <f aca="false">J14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="13" t="n">
+        <v>216</v>
+      </c>
+      <c r="C16" s="19" t="n">
         <f aca="false">C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="19" t="n">
         <f aca="false">MAX(0,D14+D10)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="19" t="n">
         <f aca="false">MAX(0,E14+E10)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="19" t="n">
         <f aca="false">MAX(0,F14+F10)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="19" t="n">
         <f aca="false">MAX(0,G14+G10)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="19" t="n">
         <f aca="false">MAX(0,H14+H10)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="19" t="n">
         <f aca="false">MAX(0,I14+I10)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="19" t="n">
         <f aca="false">MAX(0,J14+J10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="13" t="n">
+        <v>217</v>
+      </c>
+      <c r="C17" s="19" t="n">
         <f aca="false">'Sources &amp; Uses'!F6</f>
         <v>567</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="19" t="n">
         <f aca="false">C21</f>
         <v>567</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="19" t="n">
         <f aca="false">D21</f>
         <v>525.04875</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="19" t="n">
         <f aca="false">E21</f>
         <v>472.341991992188</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="19" t="n">
         <f aca="false">F21</f>
         <v>409.383413647064</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="19" t="n">
         <f aca="false">G21</f>
         <v>335.115763362686</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="19" t="n">
         <f aca="false">H21</f>
         <v>248.287150954235</v>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="19" t="n">
         <f aca="false">I21</f>
         <v>147.522090992643</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="13" t="n">
+        <v>218</v>
+      </c>
+      <c r="D18" s="19" t="n">
         <f aca="false">D17*Assumptions!$E$20</f>
         <v>48.195</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="19" t="n">
         <f aca="false">E17*Assumptions!$E$20</f>
         <v>44.62914375</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="19" t="n">
         <f aca="false">F17*Assumptions!$E$20</f>
         <v>40.149069319336</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="19" t="n">
         <f aca="false">G17*Assumptions!$E$20</f>
         <v>34.7975901600005</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="19" t="n">
         <f aca="false">H17*Assumptions!$E$20</f>
         <v>28.4848398858283</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="I18" s="19" t="n">
         <f aca="false">I17*Assumptions!$E$20</f>
         <v>21.10440783111</v>
       </c>
-      <c r="J18" s="13" t="n">
+      <c r="J18" s="19" t="n">
         <f aca="false">J17*Assumptions!$E$20</f>
         <v>12.5393777343747</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="13" t="n">
+        <v>219</v>
+      </c>
+      <c r="D19" s="19" t="n">
         <f aca="false">MIN(D17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>5.67</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="19" t="n">
         <f aca="false">MIN(E17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>5.67</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="19" t="n">
         <f aca="false">MIN(F17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>5.67</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="19" t="n">
         <f aca="false">MIN(G17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>5.67</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="19" t="n">
         <f aca="false">MIN(H17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>5.67</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="19" t="n">
         <f aca="false">MIN(I17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>5.67</v>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="J19" s="19" t="n">
         <f aca="false">MIN(J17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>5.67</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="C20" s="26" t="n">
+      <c r="B20" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="C20" s="32" t="n">
         <f aca="false">'Sources &amp; Uses'!F7</f>
         <v>121.5</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="32" t="n">
         <f aca="false">D11</f>
         <v>36.28125</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="32" t="n">
         <f aca="false">E11</f>
         <v>47.0367580078125</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="32" t="n">
         <f aca="false">F11</f>
         <v>57.2885783451233</v>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G20" s="32" t="n">
         <f aca="false">G11</f>
         <v>68.5976502843784</v>
       </c>
-      <c r="H20" s="26" t="n">
+      <c r="H20" s="32" t="n">
         <f aca="false">H11</f>
         <v>81.1586124084512</v>
       </c>
-      <c r="I20" s="26" t="n">
+      <c r="I20" s="32" t="n">
         <f aca="false">I11</f>
         <v>95.0950599615914</v>
       </c>
-      <c r="J20" s="26" t="n">
+      <c r="J20" s="32" t="n">
         <f aca="false">J11</f>
         <v>110.536186690953</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="13" t="n">
+        <v>221</v>
+      </c>
+      <c r="C21" s="19" t="n">
         <f aca="false">C17</f>
         <v>567</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="19" t="n">
         <f aca="false">MAX(0,D17-D19-D20)</f>
         <v>525.04875</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="19" t="n">
         <f aca="false">MAX(0,E17-E19-E20)</f>
         <v>472.341991992188</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="19" t="n">
         <f aca="false">MAX(0,F17-F19-F20)</f>
         <v>409.383413647064</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="19" t="n">
         <f aca="false">MAX(0,G17-G19-G20)</f>
         <v>335.115763362686</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="19" t="n">
         <f aca="false">MAX(0,H17-H19-H20)</f>
         <v>248.287150954235</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="I21" s="19" t="n">
         <f aca="false">MAX(0,I17-I19-I20)</f>
         <v>147.522090992643</v>
       </c>
-      <c r="J21" s="13" t="n">
+      <c r="J21" s="19" t="n">
         <f aca="false">MAX(0,J17-J19-J20)</f>
         <v>31.3159043016903</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C22" s="13" t="n">
+        <v>222</v>
+      </c>
+      <c r="C22" s="19" t="n">
         <f aca="false">'Sources &amp; Uses'!F7</f>
         <v>121.5</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="19" t="n">
         <f aca="false">C26</f>
         <v>121.5</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="19" t="n">
         <f aca="false">D26</f>
         <v>116.0746875</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="19" t="n">
         <f aca="false">E26</f>
         <v>107.797738623047</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="19" t="n">
         <f aca="false">F26</f>
         <v>96.7095261954575</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="H22" s="19" t="n">
         <f aca="false">G26</f>
         <v>82.4613994102266</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="I22" s="19" t="n">
         <f aca="false">H26</f>
         <v>64.6455882904206</v>
       </c>
-      <c r="J22" s="13" t="n">
+      <c r="J22" s="19" t="n">
         <f aca="false">I26</f>
         <v>42.8111909487354</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" s="13" t="n">
+        <v>223</v>
+      </c>
+      <c r="D23" s="19" t="n">
         <f aca="false">D22*Assumptions!$E$23</f>
         <v>13.365</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="19" t="n">
         <f aca="false">E22*Assumptions!$E$23</f>
         <v>12.768215625</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="19" t="n">
         <f aca="false">F22*Assumptions!$E$23</f>
         <v>11.8577512485352</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="19" t="n">
         <f aca="false">G22*Assumptions!$E$23</f>
         <v>10.6380478815003</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="19" t="n">
         <f aca="false">H22*Assumptions!$E$23</f>
         <v>9.07075393512493</v>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="I23" s="19" t="n">
         <f aca="false">I22*Assumptions!$E$23</f>
         <v>7.11101471194627</v>
       </c>
-      <c r="J23" s="13" t="n">
+      <c r="J23" s="19" t="n">
         <f aca="false">J22*Assumptions!$E$23</f>
         <v>4.70923100436089</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26" t="n">
+      <c r="B24" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32" t="n">
         <f aca="false">D22*Assumptions!$E$24</f>
         <v>3.645</v>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="32" t="n">
         <f aca="false">E22*Assumptions!$E$24</f>
         <v>3.482240625</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="32" t="n">
         <f aca="false">F22*Assumptions!$E$24</f>
         <v>3.23393215869141</v>
       </c>
-      <c r="G24" s="26" t="n">
+      <c r="G24" s="32" t="n">
         <f aca="false">G22*Assumptions!$E$24</f>
         <v>2.90128578586372</v>
       </c>
-      <c r="H24" s="26" t="n">
+      <c r="H24" s="32" t="n">
         <f aca="false">H22*Assumptions!$E$24</f>
         <v>2.4738419823068</v>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="32" t="n">
         <f aca="false">I22*Assumptions!$E$24</f>
         <v>1.93936764871262</v>
       </c>
-      <c r="J24" s="26" t="n">
+      <c r="J24" s="32" t="n">
         <f aca="false">J22*Assumptions!$E$24</f>
         <v>1.28433572846206</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="26" t="n">
+      <c r="B25" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25" s="32" t="n">
         <f aca="false">SUM(C16,C20,C13)</f>
         <v>141.5</v>
       </c>
-      <c r="D25" s="26" t="n">
+      <c r="D25" s="32" t="n">
         <f aca="false">D12</f>
         <v>9.0703125</v>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="32" t="n">
         <f aca="false">E12</f>
         <v>11.7591895019531</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="32" t="n">
         <f aca="false">F12</f>
         <v>14.3221445862808</v>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="32" t="n">
         <f aca="false">G12</f>
         <v>17.1494125710946</v>
       </c>
-      <c r="H25" s="26" t="n">
+      <c r="H25" s="32" t="n">
         <f aca="false">H12</f>
         <v>20.2896531021128</v>
       </c>
-      <c r="I25" s="26" t="n">
+      <c r="I25" s="32" t="n">
         <f aca="false">I12</f>
         <v>23.7737649903978</v>
       </c>
-      <c r="J25" s="26" t="n">
+      <c r="J25" s="32" t="n">
         <f aca="false">J12</f>
         <v>27.6340466727383</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="26" t="n">
+      <c r="B26" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="C26" s="32" t="n">
         <f aca="false">C22</f>
         <v>121.5</v>
       </c>
-      <c r="D26" s="26" t="n">
+      <c r="D26" s="32" t="n">
         <f aca="false">MAX(0,D22+D24-D25)</f>
         <v>116.0746875</v>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="32" t="n">
         <f aca="false">MAX(0,E22+E24-E25)</f>
         <v>107.797738623047</v>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="32" t="n">
         <f aca="false">MAX(0,F22+F24-F25)</f>
         <v>96.7095261954575</v>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="32" t="n">
         <f aca="false">MAX(0,G22+G24-G25)</f>
         <v>82.4613994102266</v>
       </c>
-      <c r="H26" s="26" t="n">
+      <c r="H26" s="32" t="n">
         <f aca="false">MAX(0,H22+H24-H25)</f>
         <v>64.6455882904206</v>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I26" s="32" t="n">
         <f aca="false">MAX(0,I22+I24-I25)</f>
         <v>42.8111909487354</v>
       </c>
-      <c r="J26" s="26" t="n">
+      <c r="J26" s="32" t="n">
         <f aca="false">MAX(0,J22+J24-J25)</f>
         <v>16.4614800044592</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="13" t="n">
+        <v>227</v>
+      </c>
+      <c r="C27" s="19" t="n">
         <f aca="false">SUM(C16,C21,C26)</f>
         <v>688.5</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="19" t="n">
         <f aca="false">SUM(D16,D21,D26)</f>
         <v>641.1234375</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="19" t="n">
         <f aca="false">SUM(E16,E21,E26)</f>
         <v>580.139730615235</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="19" t="n">
         <f aca="false">SUM(F16,F21,F26)</f>
         <v>506.092939842522</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="19" t="n">
         <f aca="false">SUM(G16,G21,G26)</f>
         <v>417.577162772913</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="19" t="n">
         <f aca="false">SUM(H16,H21,H26)</f>
         <v>312.932739244655</v>
       </c>
-      <c r="I27" s="13" t="n">
+      <c r="I27" s="19" t="n">
         <f aca="false">SUM(I16,I21,I26)</f>
         <v>190.333281941379</v>
       </c>
-      <c r="J27" s="13" t="n">
+      <c r="J27" s="19" t="n">
         <f aca="false">SUM(J16,J21,J26)</f>
         <v>47.7773843061495</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="13" t="n">
+        <v>228</v>
+      </c>
+      <c r="C28" s="19" t="n">
         <f aca="false">C27-C13</f>
         <v>668.5</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="19" t="n">
         <f aca="false">D27-D13</f>
         <v>618.1</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="19" t="n">
         <f aca="false">E27-E13</f>
         <v>556.22000078125</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F28" s="19" t="n">
         <f aca="false">F27-F13</f>
         <v>481.318891647095</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="19" t="n">
         <f aca="false">G27-G13</f>
         <v>391.860691915881</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="H28" s="19" t="n">
         <f aca="false">H27-H13</f>
         <v>286.169521543951</v>
       </c>
-      <c r="I28" s="13" t="n">
+      <c r="I28" s="19" t="n">
         <f aca="false">I27-I13</f>
         <v>162.408693611246</v>
       </c>
-      <c r="J28" s="13" t="n">
+      <c r="J28" s="19" t="n">
         <f aca="false">J27-J13</f>
         <v>18.5660354152367</v>
       </c>
@@ -4121,7 +6345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4136,7 +6360,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>130</v>
+        <v>229</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4147,298 +6371,298 @@
       <c r="I2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>90</v>
+      <c r="B4" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="20" t="n">
+        <v>231</v>
+      </c>
+      <c r="C5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!D25/'Operating Model'!D8,0)</f>
         <v>0.0521304797620587</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!E25/'Operating Model'!E8,0)</f>
         <v>0.0629721756094424</v>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!F25/'Operating Model'!F8,0)</f>
         <v>0.0715125166025144</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!G25/'Operating Model'!G8,0)</f>
         <v>0.0798935247080636</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!H25/'Operating Model'!H8,0)</f>
         <v>0.0882463597014973</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!I25/'Operating Model'!I8,0)</f>
         <v>0.0965913905764718</v>
       </c>
-      <c r="I5" s="20" t="n">
+      <c r="I5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!J25/'Operating Model'!J8,0)</f>
         <v>0.104942035638518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="20" t="n">
+        <v>232</v>
+      </c>
+      <c r="C6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="I6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="20" t="n">
+        <v>233</v>
+      </c>
+      <c r="C7" s="26" t="n">
         <f aca="false">C6-C5</f>
         <v>6.94786952023794</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="26" t="n">
         <f aca="false">D6-D5</f>
         <v>6.93702782439056</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="26" t="n">
         <f aca="false">E6-E5</f>
         <v>6.92848748339749</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="26" t="n">
         <f aca="false">F6-F5</f>
         <v>6.92010647529194</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="26" t="n">
         <f aca="false">G6-G5</f>
         <v>6.9117536402985</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="26" t="n">
         <f aca="false">H6-H5</f>
         <v>6.90340860942353</v>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="I7" s="26" t="n">
         <f aca="false">I6-I5</f>
         <v>6.89505796436148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="20" t="n">
+        <v>234</v>
+      </c>
+      <c r="C8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!D8/'Debt Schedule'!D7,0)</f>
         <v>2.82638888888889</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!E8/'Debt Schedule'!E7,0)</f>
         <v>3.25339487797647</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!F8/'Debt Schedule'!F7,0)</f>
         <v>3.8509305654656</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!G8/'Debt Schedule'!G7,0)</f>
         <v>4.72433880902995</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!H8/'Debt Schedule'!H7,0)</f>
         <v>6.12213905052735</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!I8/'Debt Schedule'!I7,0)</f>
         <v>8.72314292726238</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!J8/'Debt Schedule'!J7,0)</f>
         <v>15.2665509539761</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="20" t="n">
+        <v>235</v>
+      </c>
+      <c r="C9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="20" t="n">
+        <v>236</v>
+      </c>
+      <c r="C10" s="26" t="n">
         <f aca="false">C8-C9</f>
         <v>1.07638888888889</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="26" t="n">
         <f aca="false">D8-D9</f>
         <v>1.50339487797647</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="26" t="n">
         <f aca="false">E8-E9</f>
         <v>2.1009305654656</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="26" t="n">
         <f aca="false">F8-F9</f>
         <v>2.97433880902995</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="26" t="n">
         <f aca="false">G8-G9</f>
         <v>4.37213905052735</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="26" t="n">
         <f aca="false">H8-H9</f>
         <v>6.97314292726238</v>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="I10" s="26" t="n">
         <f aca="false">I8-I9</f>
         <v>13.5165509539761</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="13" t="n">
+        <v>142</v>
+      </c>
+      <c r="C11" s="19" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="19" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="19" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="19" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="19" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="19" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="13" t="n">
+        <v>237</v>
+      </c>
+      <c r="C12" s="19" t="n">
         <f aca="false">'Debt Schedule'!D13-C11</f>
         <v>3.0234375</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="19" t="n">
         <f aca="false">'Debt Schedule'!E13-D11</f>
         <v>3.91972983398437</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="19" t="n">
         <f aca="false">'Debt Schedule'!F13-E11</f>
         <v>4.77404819542694</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="19" t="n">
         <f aca="false">'Debt Schedule'!G13-F11</f>
         <v>5.71647085703153</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="19" t="n">
         <f aca="false">'Debt Schedule'!H13-G11</f>
         <v>6.76321770070426</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="19" t="n">
         <f aca="false">'Debt Schedule'!I13-H11</f>
         <v>7.92458833013261</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="19" t="n">
         <f aca="false">'Debt Schedule'!J13-I11</f>
         <v>9.21134889091276</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="str">
         <f aca="false">IF(AND(C7&gt;=0,C10&gt;=0,C12&gt;=0),"PASS","BREACH")</f>
@@ -4495,800 +6719,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:E9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <f aca="false">Assumptions!E30</f>
-        <v>0.1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <f aca="false">1-C5</f>
-        <v>0.9</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <f aca="false">'Sources &amp; Uses'!F8</f>
-        <v>1083.9</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <f aca="false">C7*(1+Assumptions!E31)^Assumptions!E29</f>
-        <v>1857.61412493012</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <f aca="false">Assumptions!E32</f>
-        <v>0.2</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:E2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:J15"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <f aca="false">'Operating Model'!D8</f>
-        <v>173.9925</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <f aca="false">'Operating Model'!E8</f>
-        <v>186.736275</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <f aca="false">'Operating Model'!F8</f>
-        <v>200.2746549375</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <f aca="false">'Operating Model'!G8</f>
-        <v>214.6533481125</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <f aca="false">'Operating Model'!H8</f>
-        <v>229.920567497002</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <f aca="false">'Operating Model'!I8</f>
-        <v>246.12716359618</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <f aca="false">'Operating Model'!J8</f>
-        <v>263.326764195104</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <f aca="false">INDEX(C5:I5,1,Assumptions!E29)</f>
-        <v>263.326764195104</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <f aca="false">Assumptions!$E$28</f>
-        <v>10</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <f aca="false">Assumptions!$E$28</f>
-        <v>10</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <f aca="false">Assumptions!$E$28</f>
-        <v>10</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <f aca="false">Assumptions!$E$28</f>
-        <v>10</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <f aca="false">Assumptions!$E$28</f>
-        <v>10</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <f aca="false">Assumptions!$E$28</f>
-        <v>10</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <f aca="false">Assumptions!$E$28</f>
-        <v>10</v>
-      </c>
-      <c r="J6" s="20" t="n">
-        <f aca="false">INDEX(C6:I6,1,Assumptions!E29)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <f aca="false">C5*C6</f>
-        <v>1739.925</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <f aca="false">D5*D6</f>
-        <v>1867.36275</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <f aca="false">E5*E6</f>
-        <v>2002.746549375</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <f aca="false">F5*F6</f>
-        <v>2146.533481125</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <f aca="false">G5*G6</f>
-        <v>2299.20567497002</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <f aca="false">H5*H6</f>
-        <v>2461.2716359618</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <f aca="false">I5*I6</f>
-        <v>2633.26764195104</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <f aca="false">INDEX(C7:I7,1,Assumptions!E29)</f>
-        <v>2633.26764195104</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <f aca="false">'Debt Schedule'!D28</f>
-        <v>618.1</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <f aca="false">'Debt Schedule'!E28</f>
-        <v>556.22000078125</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <f aca="false">'Debt Schedule'!F28</f>
-        <v>481.318891647095</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <f aca="false">'Debt Schedule'!G28</f>
-        <v>391.860691915881</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <f aca="false">'Debt Schedule'!H28</f>
-        <v>286.169521543951</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <f aca="false">'Debt Schedule'!I28</f>
-        <v>162.408693611246</v>
-      </c>
-      <c r="I8" s="13" t="n">
-        <f aca="false">'Debt Schedule'!J28</f>
-        <v>18.5660354152367</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <f aca="false">INDEX(C8:I8,1,Assumptions!E29)</f>
-        <v>18.5660354152367</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <f aca="false">MAX(0,C7-C8)</f>
-        <v>1121.825</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <f aca="false">MAX(0,D7-D8)</f>
-        <v>1311.14274921875</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <f aca="false">MAX(0,E7-E8)</f>
-        <v>1521.4276577279</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <f aca="false">MAX(0,F7-F8)</f>
-        <v>1754.67278920912</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <f aca="false">MAX(0,G7-G8)</f>
-        <v>2013.03615342606</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <f aca="false">MAX(0,H7-H8)</f>
-        <v>2298.86294235056</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <f aca="false">MAX(0,I7-I8)</f>
-        <v>2614.7016065358</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <f aca="false">INDEX(C9:I9,1,Assumptions!E29)</f>
-        <v>2614.7016065358</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^1</f>
-        <v>1170.612</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^2</f>
-        <v>1264.26096</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^3</f>
-        <v>1365.4018368</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^4</f>
-        <v>1474.633983744</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^5</f>
-        <v>1592.60470244352</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^6</f>
-        <v>1720.013078639</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^7</f>
-        <v>1857.61412493012</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <f aca="false">INDEX(C10:I10,1,Assumptions!E29)</f>
-        <v>1857.61412493012</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <f aca="false">MAX(0,C9-C10)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <f aca="false">MAX(0,D9-D10)</f>
-        <v>46.8817892187492</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <f aca="false">MAX(0,E9-E10)</f>
-        <v>156.025820927905</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <f aca="false">MAX(0,F9-F10)</f>
-        <v>280.038805465118</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <f aca="false">MAX(0,G9-G10)</f>
-        <v>420.431450982544</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <f aca="false">MAX(0,H9-H10)</f>
-        <v>578.849863711556</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <f aca="false">MAX(0,I9-I10)</f>
-        <v>757.08748160568</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <f aca="false">INDEX(C11:I11,1,Assumptions!E29)</f>
-        <v>757.08748160568</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <f aca="false">MIN(C9,C9*Assumptions!$E$30+C11*Assumptions!$E$32)</f>
-        <v>112.1825</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <f aca="false">MIN(D9,D9*Assumptions!$E$30+D11*Assumptions!$E$32)</f>
-        <v>140.490632765625</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <f aca="false">MIN(E9,E9*Assumptions!$E$30+E11*Assumptions!$E$32)</f>
-        <v>183.347929958371</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <f aca="false">MIN(F9,F9*Assumptions!$E$30+F11*Assumptions!$E$32)</f>
-        <v>231.475040013935</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <f aca="false">MIN(G9,G9*Assumptions!$E$30+G11*Assumptions!$E$32)</f>
-        <v>285.389905539115</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <f aca="false">MIN(H9,H9*Assumptions!$E$30+H11*Assumptions!$E$32)</f>
-        <v>345.656266977367</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <f aca="false">MIN(I9,I9*Assumptions!$E$30+I11*Assumptions!$E$32)</f>
-        <v>412.887656974716</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <f aca="false">INDEX(C12:I12,1,Assumptions!E29)</f>
-        <v>412.887656974716</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <f aca="false">MAX(0,C9-C12)</f>
-        <v>1009.6425</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <f aca="false">MAX(0,D9-D12)</f>
-        <v>1170.65211645312</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <f aca="false">MAX(0,E9-E12)</f>
-        <v>1338.07972776953</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <f aca="false">MAX(0,F9-F12)</f>
-        <v>1523.19774919518</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <f aca="false">MAX(0,G9-G12)</f>
-        <v>1727.64624788695</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <f aca="false">MAX(0,H9-H12)</f>
-        <v>1953.20667537319</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <f aca="false">MAX(0,I9-I12)</f>
-        <v>2201.81394956109</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <f aca="false">INDEX(C13:I13,1,Assumptions!E29)</f>
-        <v>2201.81394956109</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <f aca="false">IFERROR(C13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.93149045114863</v>
-      </c>
-      <c r="D14" s="20" t="n">
-        <f aca="false">IFERROR(D13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.0800370112124</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <f aca="false">IFERROR(E13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.23450477698084</v>
-      </c>
-      <c r="F14" s="20" t="n">
-        <f aca="false">IFERROR(F13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.40529361490468</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <f aca="false">IFERROR(G13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.59391664165232</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <f aca="false">IFERROR(H13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.80201741431238</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <f aca="false">IFERROR(I13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>2.03138107718524</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <f aca="false">INDEX(C14:I14,1,Assumptions!E29)</f>
-        <v>2.03138107718524</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <f aca="false">IFERROR((C13/'Sources &amp; Uses'!$F$8)^(1/1)-1,0)</f>
-        <v>-0.0685095488513703</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <f aca="false">IFERROR((D13/'Sources &amp; Uses'!$F$8)^(1/2)-1,0)</f>
-        <v>0.0392482914166392</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <f aca="false">IFERROR((E13/'Sources &amp; Uses'!$F$8)^(1/3)-1,0)</f>
-        <v>0.07274769884445</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <f aca="false">IFERROR((F13/'Sources &amp; Uses'!$F$8)^(1/4)-1,0)</f>
-        <v>0.0887840955006745</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <f aca="false">IFERROR((G13/'Sources &amp; Uses'!$F$8)^(1/5)-1,0)</f>
-        <v>0.0977239027592107</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <f aca="false">IFERROR((H13/'Sources &amp; Uses'!$F$8)^(1/6)-1,0)</f>
-        <v>0.103129496380244</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <f aca="false">IFERROR((I13/'Sources &amp; Uses'!$F$8)^(1/7)-1,0)</f>
-        <v>0.106547854276197</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <f aca="false">INDEX(C15:I15,1,Assumptions!E29)</f>
-        <v>0.106547854276197</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:J2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0759620362720157</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.113835763725601</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.147164780213708</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.177017888195313</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.204117616094705</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0351695155188243</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0716073514064728</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.10367277814797</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.132394077119746</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.158466383813301</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.00219075882595887</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0374677466533251</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0685116229232259</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0963179096999034</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.121559596629277</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0253434630919046</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.00896432360994903</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0391552994006961</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0661976353385956</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0907458313298675</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0488831509456008</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.015403958275933</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0140578517839125</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.040447067240178</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0644023806629515</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:G9">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFFCE4D6"/>
-        <color rgb="FFFFF2CC"/>
-        <color rgb="FFE2F0D9"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>